--- a/tabular/refseq-lineage/ifnl-curated-side-data-mammalia-b.xlsx
+++ b/tabular/refseq-lineage/ifnl-curated-side-data-mammalia-b.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/host/IFNL-Evolution/tabular/refseq-lineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45093ABB-1309-C54F-B384-DB42E0AC4AAC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EF0B9A-25E3-EE46-ADC2-1E89F2E5566C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="500" windowWidth="27900" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2599" uniqueCount="619">
   <si>
     <t>retroIFNL1a</t>
   </si>
@@ -1013,9 +1013,6 @@
     <t>XM_006096748</t>
   </si>
   <si>
-    <t>XM_006540121</t>
-  </si>
-  <si>
     <t>XM_006540130</t>
   </si>
   <si>
@@ -1574,9 +1571,6 @@
     <t>Placental2_Rodent1</t>
   </si>
   <si>
-    <t>NK_Rodent1</t>
-  </si>
-  <si>
     <t>XM_036323965</t>
   </si>
   <si>
@@ -1809,9 +1803,6 @@
   </si>
   <si>
     <t>Placental2_Haplorhine-1.2</t>
-  </si>
-  <si>
-    <t>NK_Rodent-2.1</t>
   </si>
   <si>
     <t>Placental2_Rodent-2.1</t>
@@ -3626,7 +3617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S141"/>
+  <dimension ref="A1:S140"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
@@ -3655,49 +3646,49 @@
         <v>212</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D1" s="18" t="s">
         <v>267</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F1" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="G1" s="18" t="s">
         <v>486</v>
       </c>
-      <c r="G1" s="18" t="s">
-        <v>487</v>
-      </c>
       <c r="H1" s="18" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I1" s="35" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="J1" s="35" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="K1" s="35" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="L1" s="18" t="s">
         <v>264</v>
       </c>
       <c r="M1" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="O1" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="N1" s="18" t="s">
-        <v>395</v>
-      </c>
-      <c r="O1" s="18" t="s">
+      <c r="P1" s="18" t="s">
         <v>372</v>
-      </c>
-      <c r="P1" s="18" t="s">
-        <v>373</v>
       </c>
       <c r="Q1" s="19" t="s">
         <v>265</v>
@@ -3714,25 +3705,25 @@
         <v>2</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C2" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F2" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H2" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I2" s="34">
         <v>1.1000000000000001</v>
@@ -3766,28 +3757,28 @@
     </row>
     <row r="3" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C3" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I3" s="34">
         <v>1.1000000000000001</v>
@@ -3799,7 +3790,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M3" s="23" t="s">
         <v>57</v>
@@ -3811,7 +3802,7 @@
         <v>80</v>
       </c>
       <c r="P3" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Q3" s="23"/>
       <c r="R3" s="23"/>
@@ -3824,25 +3815,25 @@
         <v>172</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C4" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I4" s="34">
         <v>1.1000000000000001</v>
@@ -3880,28 +3871,28 @@
     </row>
     <row r="5" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I5" s="39">
         <v>1.1000000000000001</v>
@@ -3913,7 +3904,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="26" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M5" s="26" t="s">
         <v>57</v>
@@ -3925,7 +3916,7 @@
         <v>55</v>
       </c>
       <c r="P5" s="26" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q5" s="26"/>
       <c r="R5" s="26"/>
@@ -3933,28 +3924,28 @@
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C6" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I6" s="39">
         <v>1.1000000000000001</v>
@@ -3986,28 +3977,28 @@
     </row>
     <row r="7" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C7" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I7" s="39">
         <v>1.1000000000000001</v>
@@ -4019,7 +4010,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="26" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="M7" s="26" t="s">
         <v>57</v>
@@ -4031,7 +4022,7 @@
         <v>80</v>
       </c>
       <c r="P7" s="26" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Q7" s="26"/>
       <c r="R7" s="26"/>
@@ -4039,28 +4030,28 @@
     </row>
     <row r="8" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I8" s="39">
         <v>1.1000000000000001</v>
@@ -4092,28 +4083,28 @@
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C9" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I9" s="39">
         <v>1.1000000000000001</v>
@@ -4125,7 +4116,7 @@
         <v>1</v>
       </c>
       <c r="L9" s="26" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M9" s="26" t="s">
         <v>57</v>
@@ -4145,28 +4136,28 @@
     </row>
     <row r="10" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C10" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I10" s="39">
         <v>1.1000000000000001</v>
@@ -4178,7 +4169,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="26" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="M10" s="26" t="s">
         <v>57</v>
@@ -4190,7 +4181,7 @@
         <v>80</v>
       </c>
       <c r="P10" s="26" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q10" s="26"/>
       <c r="R10" s="26"/>
@@ -4198,28 +4189,28 @@
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C11" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I11" s="39">
         <v>1.1000000000000001</v>
@@ -4231,7 +4222,7 @@
         <v>1</v>
       </c>
       <c r="L11" s="26" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M11" s="26" t="s">
         <v>57</v>
@@ -4243,7 +4234,7 @@
         <v>80</v>
       </c>
       <c r="P11" s="26" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q11" s="26"/>
       <c r="R11" s="26"/>
@@ -4251,28 +4242,28 @@
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C12" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I12" s="39">
         <v>1.1000000000000001</v>
@@ -4284,7 +4275,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M12" s="26" t="s">
         <v>57</v>
@@ -4304,28 +4295,28 @@
     </row>
     <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C13" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I13" s="39">
         <v>1.1000000000000001</v>
@@ -4337,7 +4328,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="26" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M13" s="26" t="s">
         <v>57</v>
@@ -4349,7 +4340,7 @@
         <v>80</v>
       </c>
       <c r="P13" s="26" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q13" s="26"/>
       <c r="R13" s="26"/>
@@ -4357,28 +4348,28 @@
     </row>
     <row r="14" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C14" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I14" s="39">
         <v>1.1000000000000001</v>
@@ -4390,7 +4381,7 @@
         <v>2</v>
       </c>
       <c r="L14" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M14" s="26" t="s">
         <v>57</v>
@@ -4402,7 +4393,7 @@
         <v>80</v>
       </c>
       <c r="P14" s="26" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q14" s="26"/>
       <c r="R14" s="26"/>
@@ -4410,28 +4401,28 @@
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C15" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I15" s="34">
         <v>1.1000000000000001</v>
@@ -4443,7 +4434,7 @@
         <v>2</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M15" s="23" t="s">
         <v>57</v>
@@ -4463,28 +4454,28 @@
     </row>
     <row r="16" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I16" s="34">
         <v>1.1000000000000001</v>
@@ -4496,7 +4487,7 @@
         <v>2</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M16" s="23" t="s">
         <v>57</v>
@@ -4508,7 +4499,7 @@
         <v>80</v>
       </c>
       <c r="P16" s="23" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Q16" s="23"/>
       <c r="R16" s="23"/>
@@ -4516,28 +4507,28 @@
     </row>
     <row r="17" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C17" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I17" s="34">
         <v>1.1000000000000001</v>
@@ -4549,7 +4540,7 @@
         <v>2</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M17" s="23" t="s">
         <v>57</v>
@@ -4561,7 +4552,7 @@
         <v>80</v>
       </c>
       <c r="P17" s="23" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q17" s="23"/>
       <c r="R17" s="23"/>
@@ -4569,28 +4560,28 @@
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I18" s="34">
         <v>1.1000000000000001</v>
@@ -4602,7 +4593,7 @@
         <v>2</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M18" s="23" t="s">
         <v>57</v>
@@ -4614,7 +4605,7 @@
         <v>80</v>
       </c>
       <c r="P18" s="23" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q18" s="23"/>
       <c r="R18" s="23"/>
@@ -4622,28 +4613,28 @@
     </row>
     <row r="19" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C19" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I19" s="34">
         <v>1.1000000000000001</v>
@@ -4655,7 +4646,7 @@
         <v>2</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M19" s="23" t="s">
         <v>57</v>
@@ -4667,7 +4658,7 @@
         <v>80</v>
       </c>
       <c r="P19" s="23" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q19" s="23"/>
       <c r="R19" s="23"/>
@@ -4675,28 +4666,28 @@
     </row>
     <row r="20" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C20" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I20" s="34">
         <v>1.1000000000000001</v>
@@ -4708,7 +4699,7 @@
         <v>2</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M20" s="23" t="s">
         <v>57</v>
@@ -4720,7 +4711,7 @@
         <v>80</v>
       </c>
       <c r="P20" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Q20" s="23"/>
       <c r="R20" s="23"/>
@@ -4728,28 +4719,28 @@
     </row>
     <row r="21" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C21" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I21" s="34">
         <v>1.1000000000000001</v>
@@ -4784,25 +4775,25 @@
         <v>247</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C22" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I22" s="34">
         <v>1.1000000000000001</v>
@@ -4833,33 +4824,33 @@
       </c>
       <c r="R22" s="23"/>
       <c r="S22" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C23" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I23" s="34">
         <v>1.1000000000000001</v>
@@ -4871,7 +4862,7 @@
         <v>2</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M23" s="23" t="s">
         <v>57</v>
@@ -4891,28 +4882,28 @@
     </row>
     <row r="24" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C24" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I24" s="34">
         <v>1.1000000000000001</v>
@@ -4924,7 +4915,7 @@
         <v>2</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M24" s="23" t="s">
         <v>57</v>
@@ -4944,28 +4935,28 @@
     </row>
     <row r="25" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C25" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I25" s="34">
         <v>1.1000000000000001</v>
@@ -4997,28 +4988,28 @@
     </row>
     <row r="26" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C26" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I26" s="34">
         <v>1.1000000000000001</v>
@@ -5030,7 +5021,7 @@
         <v>2</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M26" s="23" t="s">
         <v>57</v>
@@ -5042,7 +5033,7 @@
         <v>55</v>
       </c>
       <c r="P26" s="23" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q26" s="23"/>
       <c r="R26" s="23"/>
@@ -5050,28 +5041,28 @@
     </row>
     <row r="27" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C27" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I27" s="34">
         <v>1.1000000000000001</v>
@@ -5083,7 +5074,7 @@
         <v>2</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M27" s="23" t="s">
         <v>57</v>
@@ -5095,7 +5086,7 @@
         <v>55</v>
       </c>
       <c r="P27" s="23" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q27" s="23"/>
       <c r="R27" s="23"/>
@@ -5103,28 +5094,28 @@
     </row>
     <row r="28" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C28" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I28" s="34">
         <v>1.1000000000000001</v>
@@ -5136,7 +5127,7 @@
         <v>2</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M28" s="23" t="s">
         <v>57</v>
@@ -5148,7 +5139,7 @@
         <v>80</v>
       </c>
       <c r="P28" s="23" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q28" s="23"/>
       <c r="R28" s="23"/>
@@ -5156,28 +5147,28 @@
     </row>
     <row r="29" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C29" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I29" s="34">
         <v>1.1000000000000001</v>
@@ -5189,7 +5180,7 @@
         <v>2</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M29" s="23" t="s">
         <v>57</v>
@@ -5201,7 +5192,7 @@
         <v>80</v>
       </c>
       <c r="P29" s="23" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q29" s="23"/>
       <c r="R29" s="23"/>
@@ -5209,28 +5200,28 @@
     </row>
     <row r="30" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C30" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I30" s="34">
         <v>1.1000000000000001</v>
@@ -5242,7 +5233,7 @@
         <v>2</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M30" s="23" t="s">
         <v>57</v>
@@ -5254,7 +5245,7 @@
         <v>80</v>
       </c>
       <c r="P30" s="23" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Q30" s="23"/>
       <c r="R30" s="23"/>
@@ -5262,28 +5253,28 @@
     </row>
     <row r="31" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G31" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I31" s="34">
         <v>1.1000000000000001</v>
@@ -5295,7 +5286,7 @@
         <v>2</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M31" s="23" t="s">
         <v>57</v>
@@ -5307,7 +5298,7 @@
         <v>80</v>
       </c>
       <c r="P31" s="23" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
@@ -5318,25 +5309,25 @@
         <v>211</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I32" s="34">
         <v>1.1000000000000001</v>
@@ -5370,28 +5361,28 @@
     </row>
     <row r="33" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C33" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G33" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I33" s="34">
         <v>1.1000000000000001</v>
@@ -5403,7 +5394,7 @@
         <v>2</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M33" s="23" t="s">
         <v>57</v>
@@ -5415,7 +5406,7 @@
         <v>80</v>
       </c>
       <c r="P33" s="23" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q33" s="23"/>
       <c r="R33" s="23"/>
@@ -5423,28 +5414,28 @@
     </row>
     <row r="34" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C34" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F34" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G34" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H34" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I34" s="34">
         <v>1.1000000000000001</v>
@@ -5456,7 +5447,7 @@
         <v>2</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M34" s="23" t="s">
         <v>57</v>
@@ -5478,28 +5469,28 @@
     </row>
     <row r="35" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C35" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G35" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H35" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I35" s="34">
         <v>1.1000000000000001</v>
@@ -5511,7 +5502,7 @@
         <v>2</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M35" s="23" t="s">
         <v>57</v>
@@ -5533,28 +5524,28 @@
     </row>
     <row r="36" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C36" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G36" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H36" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I36" s="34">
         <v>1.1000000000000001</v>
@@ -5566,7 +5557,7 @@
         <v>2</v>
       </c>
       <c r="L36" s="23" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M36" s="23" t="s">
         <v>57</v>
@@ -5578,7 +5569,7 @@
         <v>55</v>
       </c>
       <c r="P36" s="23" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q36" s="23"/>
       <c r="R36" s="23"/>
@@ -5586,28 +5577,28 @@
     </row>
     <row r="37" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C37" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G37" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I37" s="34">
         <v>1.1000000000000001</v>
@@ -5619,7 +5610,7 @@
         <v>2</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M37" s="23" t="s">
         <v>57</v>
@@ -5631,7 +5622,7 @@
         <v>80</v>
       </c>
       <c r="P37" s="23" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="Q37" s="23"/>
       <c r="R37" s="23"/>
@@ -5639,28 +5630,28 @@
     </row>
     <row r="38" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C38" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F38" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G38" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H38" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I38" s="34">
         <v>1.1000000000000001</v>
@@ -5692,28 +5683,28 @@
     </row>
     <row r="39" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C39" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G39" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I39" s="39">
         <v>1.1000000000000001</v>
@@ -5745,28 +5736,28 @@
     </row>
     <row r="40" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C40" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G40" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I40" s="39">
         <v>1.1000000000000001</v>
@@ -5778,7 +5769,7 @@
         <v>2</v>
       </c>
       <c r="L40" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M40" s="26" t="s">
         <v>57</v>
@@ -5801,25 +5792,25 @@
         <v>208</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C41" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F41" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G41" s="23" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I41" s="34">
         <v>1.1000000000000001</v>
@@ -5853,28 +5844,28 @@
     </row>
     <row r="42" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B42" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C42" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I42" s="39">
         <v>1.1000000000000001</v>
@@ -5886,7 +5877,7 @@
         <v>2</v>
       </c>
       <c r="L42" s="26" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M42" s="26" t="s">
         <v>57</v>
@@ -5898,7 +5889,7 @@
         <v>96</v>
       </c>
       <c r="P42" s="26" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q42" s="26"/>
       <c r="R42" s="26"/>
@@ -5906,28 +5897,28 @@
     </row>
     <row r="43" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C43" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G43" s="26" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I43" s="39">
         <v>1.1000000000000001</v>
@@ -5939,7 +5930,7 @@
         <v>2</v>
       </c>
       <c r="L43" s="23" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M43" s="23" t="s">
         <v>57</v>
@@ -5948,10 +5939,10 @@
         <v>56</v>
       </c>
       <c r="O43" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="P43" s="23" t="s">
         <v>483</v>
-      </c>
-      <c r="P43" s="23" t="s">
-        <v>484</v>
       </c>
       <c r="Q43" s="28"/>
       <c r="R43" s="28"/>
@@ -5959,28 +5950,28 @@
     </row>
     <row r="44" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C44" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I44" s="34">
         <v>1.2</v>
@@ -5992,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="L44" s="23" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M44" s="23" t="s">
         <v>57</v>
@@ -6004,7 +5995,7 @@
         <v>96</v>
       </c>
       <c r="P44" s="23" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Q44" s="23"/>
       <c r="R44" s="23"/>
@@ -6015,25 +6006,25 @@
         <v>183</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C45" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I45" s="34">
         <v>1.2</v>
@@ -6067,28 +6058,28 @@
     </row>
     <row r="46" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C46" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I46" s="34">
         <v>1.2</v>
@@ -6100,7 +6091,7 @@
         <v>2</v>
       </c>
       <c r="L46" s="23" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M46" s="23" t="s">
         <v>57</v>
@@ -6120,28 +6111,28 @@
     </row>
     <row r="47" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C47" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I47" s="34">
         <v>1.2</v>
@@ -6153,7 +6144,7 @@
         <v>2</v>
       </c>
       <c r="L47" s="23" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M47" s="23" t="s">
         <v>57</v>
@@ -6162,10 +6153,10 @@
         <v>56</v>
       </c>
       <c r="O47" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="P47" s="23" t="s">
         <v>483</v>
-      </c>
-      <c r="P47" s="23" t="s">
-        <v>484</v>
       </c>
       <c r="Q47" s="23"/>
       <c r="R47" s="23"/>
@@ -6176,25 +6167,25 @@
         <v>2</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C48" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I48" s="34">
         <v>1.2</v>
@@ -6228,28 +6219,28 @@
     </row>
     <row r="49" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C49" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I49" s="34">
         <v>1.2</v>
@@ -6261,7 +6252,7 @@
         <v>2</v>
       </c>
       <c r="L49" s="23" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M49" s="23" t="s">
         <v>57</v>
@@ -6281,28 +6272,28 @@
     </row>
     <row r="50" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C50" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I50" s="34">
         <v>1.2</v>
@@ -6314,7 +6305,7 @@
         <v>2</v>
       </c>
       <c r="L50" s="23" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M50" s="23" t="s">
         <v>57</v>
@@ -6326,7 +6317,7 @@
         <v>96</v>
       </c>
       <c r="P50" s="23" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q50" s="23"/>
       <c r="R50" s="23"/>
@@ -6334,28 +6325,28 @@
     </row>
     <row r="51" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>325</v>
+        <v>5</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C51" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F51" s="23" t="s">
         <v>499</v>
       </c>
       <c r="G51" s="23" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H51" s="23" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I51" s="34">
         <v>2.1</v>
@@ -6367,7 +6358,7 @@
         <v>1</v>
       </c>
       <c r="L51" s="23" t="s">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="M51" s="23" t="s">
         <v>57</v>
@@ -6376,41 +6367,41 @@
         <v>62</v>
       </c>
       <c r="O51" s="23" t="s">
-        <v>387</v>
+        <v>66</v>
       </c>
       <c r="P51" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q51" s="23"/>
+        <v>65</v>
+      </c>
+      <c r="Q51" s="23" t="s">
+        <v>5</v>
+      </c>
       <c r="R51" s="23"/>
-      <c r="S51" s="23" t="s">
-        <v>312</v>
-      </c>
+      <c r="S51" s="23"/>
     </row>
     <row r="52" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>5</v>
+        <v>187</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C52" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H52" s="23" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I52" s="34">
         <v>2.1</v>
@@ -6422,7 +6413,7 @@
         <v>1</v>
       </c>
       <c r="L52" s="23" t="s">
-        <v>215</v>
+        <v>155</v>
       </c>
       <c r="M52" s="23" t="s">
         <v>57</v>
@@ -6431,41 +6422,41 @@
         <v>62</v>
       </c>
       <c r="O52" s="23" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="P52" s="23" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="Q52" s="23" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="R52" s="23"/>
       <c r="S52" s="23"/>
     </row>
     <row r="53" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
-        <v>187</v>
+        <v>276</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C53" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F53" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G53" s="23" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I53" s="34">
         <v>2.1</v>
@@ -6491,36 +6482,34 @@
       <c r="P53" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="Q53" s="23" t="s">
-        <v>48</v>
-      </c>
+      <c r="Q53" s="23"/>
       <c r="R53" s="23"/>
       <c r="S53" s="23"/>
     </row>
     <row r="54" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
-        <v>276</v>
+        <v>185</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C54" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F54" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G54" s="23" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H54" s="23" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I54" s="34">
         <v>2.1</v>
@@ -6532,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="L54" s="23" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M54" s="23" t="s">
         <v>57</v>
@@ -6541,39 +6530,41 @@
         <v>62</v>
       </c>
       <c r="O54" s="23" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="P54" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q54" s="23"/>
+        <v>97</v>
+      </c>
+      <c r="Q54" s="23" t="s">
+        <v>47</v>
+      </c>
       <c r="R54" s="23"/>
       <c r="S54" s="23"/>
     </row>
     <row r="55" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
-        <v>185</v>
+        <v>277</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C55" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F55" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G55" s="23" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I55" s="34">
         <v>2.1</v>
@@ -6585,7 +6576,7 @@
         <v>1</v>
       </c>
       <c r="L55" s="23" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M55" s="23" t="s">
         <v>57</v>
@@ -6594,53 +6585,51 @@
         <v>62</v>
       </c>
       <c r="O55" s="23" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="P55" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q55" s="23" t="s">
-        <v>47</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="Q55" s="23"/>
       <c r="R55" s="23"/>
       <c r="S55" s="23"/>
     </row>
     <row r="56" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
-        <v>277</v>
+        <v>343</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C56" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>511</v>
-      </c>
-      <c r="F56" s="23" t="s">
+        <v>505</v>
+      </c>
+      <c r="F56" s="27" t="s">
         <v>500</v>
       </c>
-      <c r="G56" s="23" t="s">
-        <v>580</v>
+      <c r="G56" s="27" t="s">
+        <v>579</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I56" s="34">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J56" s="34">
         <v>2</v>
       </c>
       <c r="K56" s="34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L56" s="23" t="s">
-        <v>155</v>
+        <v>367</v>
       </c>
       <c r="M56" s="23" t="s">
         <v>57</v>
@@ -6649,39 +6638,41 @@
         <v>62</v>
       </c>
       <c r="O56" s="23" t="s">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="P56" s="23" t="s">
-        <v>77</v>
+        <v>289</v>
       </c>
       <c r="Q56" s="23"/>
       <c r="R56" s="23"/>
-      <c r="S56" s="23"/>
+      <c r="S56" s="23" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="57" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
-        <v>344</v>
+        <v>199</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C57" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>506</v>
-      </c>
-      <c r="F57" s="27" t="s">
-        <v>501</v>
-      </c>
-      <c r="G57" s="27" t="s">
-        <v>581</v>
+        <v>505</v>
+      </c>
+      <c r="F57" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="G57" s="23" t="s">
+        <v>579</v>
       </c>
       <c r="H57" s="23" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I57" s="34">
         <v>2.2000000000000002</v>
@@ -6693,7 +6684,7 @@
         <v>2</v>
       </c>
       <c r="L57" s="23" t="s">
-        <v>368</v>
+        <v>217</v>
       </c>
       <c r="M57" s="23" t="s">
         <v>57</v>
@@ -6702,153 +6693,151 @@
         <v>62</v>
       </c>
       <c r="O57" s="23" t="s">
-        <v>387</v>
+        <v>64</v>
       </c>
       <c r="P57" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q57" s="23"/>
+        <v>63</v>
+      </c>
+      <c r="Q57" s="23" t="s">
+        <v>34</v>
+      </c>
       <c r="R57" s="23"/>
       <c r="S57" s="23" t="s">
-        <v>312</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C58" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>593</v>
-      </c>
-      <c r="E58" s="23" t="s">
-        <v>506</v>
-      </c>
-      <c r="F58" s="23" t="s">
-        <v>501</v>
-      </c>
-      <c r="G58" s="23" t="s">
-        <v>581</v>
-      </c>
-      <c r="H58" s="23" t="s">
-        <v>554</v>
-      </c>
-      <c r="I58" s="34">
+        <v>590</v>
+      </c>
+      <c r="E58" s="26" t="s">
+        <v>505</v>
+      </c>
+      <c r="F58" s="26" t="s">
+        <v>500</v>
+      </c>
+      <c r="G58" s="26" t="s">
+        <v>579</v>
+      </c>
+      <c r="H58" s="26" t="s">
+        <v>552</v>
+      </c>
+      <c r="I58" s="39">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J58" s="34">
+      <c r="J58" s="39">
         <v>2</v>
       </c>
-      <c r="K58" s="34">
+      <c r="K58" s="39">
         <v>2</v>
       </c>
-      <c r="L58" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="M58" s="23" t="s">
+      <c r="L58" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="M58" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="N58" s="23" t="s">
+      <c r="N58" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="O58" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="P58" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q58" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="R58" s="23"/>
-      <c r="S58" s="23" t="s">
-        <v>250</v>
-      </c>
+      <c r="O58" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="P58" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q58" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="R58" s="26"/>
+      <c r="S58" s="26"/>
     </row>
     <row r="59" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
-        <v>198</v>
+        <v>297</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C59" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>593</v>
-      </c>
-      <c r="E59" s="26" t="s">
-        <v>506</v>
-      </c>
-      <c r="F59" s="26" t="s">
-        <v>501</v>
-      </c>
-      <c r="G59" s="26" t="s">
-        <v>581</v>
-      </c>
-      <c r="H59" s="26" t="s">
-        <v>554</v>
-      </c>
-      <c r="I59" s="39">
+        <v>591</v>
+      </c>
+      <c r="E59" s="23" t="s">
+        <v>510</v>
+      </c>
+      <c r="F59" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="G59" s="23" t="s">
+        <v>579</v>
+      </c>
+      <c r="H59" s="23" t="s">
+        <v>552</v>
+      </c>
+      <c r="I59" s="34">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J59" s="39">
+      <c r="J59" s="34">
         <v>2</v>
       </c>
-      <c r="K59" s="39">
+      <c r="K59" s="34">
         <v>2</v>
       </c>
-      <c r="L59" s="26" t="s">
-        <v>216</v>
-      </c>
-      <c r="M59" s="26" t="s">
+      <c r="L59" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="M59" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="N59" s="26" t="s">
+      <c r="N59" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="O59" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="P59" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q59" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="R59" s="26"/>
-      <c r="S59" s="26"/>
+      <c r="O59" s="23" t="s">
+        <v>386</v>
+      </c>
+      <c r="P59" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q59" s="23"/>
+      <c r="R59" s="23"/>
+      <c r="S59" s="23"/>
     </row>
     <row r="60" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C60" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F60" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G60" s="23" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I60" s="34">
         <v>2.2000000000000002</v>
@@ -6860,7 +6849,7 @@
         <v>2</v>
       </c>
       <c r="L60" s="23" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="M60" s="23" t="s">
         <v>57</v>
@@ -6869,7 +6858,7 @@
         <v>62</v>
       </c>
       <c r="O60" s="23" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P60" s="23" t="s">
         <v>289</v>
@@ -6880,28 +6869,28 @@
     </row>
     <row r="61" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B61" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C61" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F61" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I61" s="34">
         <v>2.2000000000000002</v>
@@ -6922,7 +6911,7 @@
         <v>62</v>
       </c>
       <c r="O61" s="23" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P61" s="23" t="s">
         <v>289</v>
@@ -6933,28 +6922,28 @@
     </row>
     <row r="62" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
-        <v>290</v>
+        <v>188</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C62" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E62" s="23" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F62" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G62" s="23" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="I62" s="34">
         <v>2.2000000000000002</v>
@@ -6966,7 +6955,7 @@
         <v>2</v>
       </c>
       <c r="L62" s="23" t="s">
-        <v>287</v>
+        <v>217</v>
       </c>
       <c r="M62" s="23" t="s">
         <v>57</v>
@@ -6975,255 +6964,253 @@
         <v>62</v>
       </c>
       <c r="O62" s="23" t="s">
-        <v>387</v>
+        <v>64</v>
       </c>
       <c r="P62" s="23" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q62" s="23"/>
+        <v>63</v>
+      </c>
+      <c r="Q62" s="23" t="s">
+        <v>33</v>
+      </c>
       <c r="R62" s="23"/>
       <c r="S62" s="23"/>
     </row>
     <row r="63" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="8" t="s">
-        <v>188</v>
+        <v>325</v>
       </c>
       <c r="B63" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C63" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>594</v>
-      </c>
-      <c r="E63" s="23" t="s">
-        <v>511</v>
-      </c>
-      <c r="F63" s="23" t="s">
-        <v>500</v>
-      </c>
-      <c r="G63" s="23" t="s">
-        <v>581</v>
-      </c>
-      <c r="H63" s="23" t="s">
-        <v>554</v>
-      </c>
-      <c r="I63" s="34">
+        <v>591</v>
+      </c>
+      <c r="E63" s="26" t="s">
+        <v>510</v>
+      </c>
+      <c r="F63" s="26" t="s">
+        <v>499</v>
+      </c>
+      <c r="G63" s="26" t="s">
+        <v>579</v>
+      </c>
+      <c r="H63" s="26" t="s">
+        <v>552</v>
+      </c>
+      <c r="I63" s="39">
         <v>2.2000000000000002</v>
       </c>
-      <c r="J63" s="34">
+      <c r="J63" s="39">
         <v>2</v>
       </c>
-      <c r="K63" s="34">
+      <c r="K63" s="39">
         <v>2</v>
       </c>
-      <c r="L63" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="M63" s="23" t="s">
+      <c r="L63" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="M63" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="N63" s="23" t="s">
+      <c r="N63" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="O63" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="P63" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q63" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="R63" s="23"/>
-      <c r="S63" s="23"/>
+      <c r="O63" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="P63" s="26" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q63" s="26"/>
+      <c r="R63" s="26"/>
+      <c r="S63" s="26" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="64" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C64" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="F64" s="26" t="s">
         <v>500</v>
       </c>
       <c r="G64" s="26" t="s">
-        <v>581</v>
+        <v>561</v>
       </c>
       <c r="H64" s="26" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I64" s="39">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
       <c r="J64" s="39">
-        <v>2</v>
-      </c>
-      <c r="K64" s="39">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K64" s="39"/>
       <c r="L64" s="26" t="s">
-        <v>287</v>
+        <v>232</v>
       </c>
       <c r="M64" s="26" t="s">
         <v>57</v>
       </c>
       <c r="N64" s="26" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="O64" s="26" t="s">
-        <v>387</v>
+        <v>100</v>
       </c>
       <c r="P64" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q64" s="26"/>
+        <v>99</v>
+      </c>
+      <c r="Q64" s="26" t="s">
+        <v>43</v>
+      </c>
       <c r="R64" s="26"/>
-      <c r="S64" s="26" t="s">
-        <v>312</v>
-      </c>
+      <c r="S64" s="26"/>
     </row>
     <row r="65" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C65" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>595</v>
-      </c>
-      <c r="E65" s="26" t="s">
-        <v>502</v>
-      </c>
-      <c r="F65" s="26" t="s">
-        <v>501</v>
-      </c>
-      <c r="G65" s="26" t="s">
-        <v>563</v>
-      </c>
-      <c r="H65" s="26" t="s">
-        <v>555</v>
-      </c>
-      <c r="I65" s="39">
+        <v>593</v>
+      </c>
+      <c r="E65" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="F65" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="G65" s="23" t="s">
+        <v>561</v>
+      </c>
+      <c r="H65" s="23" t="s">
+        <v>553</v>
+      </c>
+      <c r="I65" s="34">
         <v>3</v>
       </c>
-      <c r="J65" s="39">
+      <c r="J65" s="34">
         <v>3</v>
       </c>
-      <c r="K65" s="39"/>
-      <c r="L65" s="26" t="s">
+      <c r="K65" s="34"/>
+      <c r="L65" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="M65" s="26" t="s">
+      <c r="M65" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="N65" s="26" t="s">
+      <c r="N65" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O65" s="26" t="s">
+      <c r="O65" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="P65" s="26" t="s">
+      <c r="P65" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="Q65" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="R65" s="26"/>
-      <c r="S65" s="26"/>
+      <c r="Q65" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="R65" s="23"/>
+      <c r="S65" s="23"/>
     </row>
     <row r="66" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
-        <v>184</v>
+        <v>449</v>
       </c>
       <c r="B66" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C66" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>596</v>
-      </c>
-      <c r="E66" s="23" t="s">
-        <v>531</v>
-      </c>
-      <c r="F66" s="23" t="s">
+        <v>594</v>
+      </c>
+      <c r="E66" s="26" t="s">
+        <v>525</v>
+      </c>
+      <c r="F66" s="26" t="s">
         <v>500</v>
       </c>
-      <c r="G66" s="23" t="s">
-        <v>563</v>
-      </c>
-      <c r="H66" s="23" t="s">
-        <v>555</v>
-      </c>
-      <c r="I66" s="34">
-        <v>3</v>
-      </c>
-      <c r="J66" s="34">
-        <v>3</v>
-      </c>
-      <c r="K66" s="34"/>
-      <c r="L66" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="M66" s="23" t="s">
+      <c r="G66" s="26" t="s">
+        <v>562</v>
+      </c>
+      <c r="H66" s="26" t="s">
+        <v>554</v>
+      </c>
+      <c r="I66" s="39">
+        <v>4</v>
+      </c>
+      <c r="J66" s="39">
+        <v>4</v>
+      </c>
+      <c r="K66" s="39"/>
+      <c r="L66" s="26" t="s">
+        <v>432</v>
+      </c>
+      <c r="M66" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="N66" s="23" t="s">
+      <c r="N66" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="O66" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="P66" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q66" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="R66" s="23"/>
-      <c r="S66" s="23"/>
+      <c r="O66" s="26" t="s">
+        <v>465</v>
+      </c>
+      <c r="P66" s="26" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q66" s="26"/>
+      <c r="R66" s="26"/>
+      <c r="S66" s="30"/>
     </row>
     <row r="67" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
-        <v>450</v>
+        <v>171</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C67" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G67" s="26" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H67" s="26" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="I67" s="39">
         <v>4</v>
@@ -7233,7 +7220,7 @@
       </c>
       <c r="K67" s="39"/>
       <c r="L67" s="26" t="s">
-        <v>433</v>
+        <v>229</v>
       </c>
       <c r="M67" s="26" t="s">
         <v>57</v>
@@ -7242,39 +7229,41 @@
         <v>56</v>
       </c>
       <c r="O67" s="26" t="s">
-        <v>466</v>
+        <v>76</v>
       </c>
       <c r="P67" s="26" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q67" s="26"/>
+        <v>75</v>
+      </c>
+      <c r="Q67" s="26" t="s">
+        <v>39</v>
+      </c>
       <c r="R67" s="26"/>
-      <c r="S67" s="30"/>
+      <c r="S67" s="26"/>
     </row>
     <row r="68" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
-        <v>171</v>
+        <v>431</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C68" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E68" s="26" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G68" s="26" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H68" s="26" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="I68" s="39">
         <v>4</v>
@@ -7284,7 +7273,7 @@
       </c>
       <c r="K68" s="39"/>
       <c r="L68" s="26" t="s">
-        <v>229</v>
+        <v>432</v>
       </c>
       <c r="M68" s="26" t="s">
         <v>57</v>
@@ -7293,41 +7282,39 @@
         <v>56</v>
       </c>
       <c r="O68" s="26" t="s">
-        <v>76</v>
+        <v>465</v>
       </c>
       <c r="P68" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q68" s="26" t="s">
-        <v>39</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="Q68" s="26"/>
       <c r="R68" s="26"/>
-      <c r="S68" s="26"/>
+      <c r="S68" s="30"/>
     </row>
     <row r="69" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C69" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G69" s="26" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H69" s="26" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="I69" s="39">
         <v>4</v>
@@ -7337,7 +7324,7 @@
       </c>
       <c r="K69" s="39"/>
       <c r="L69" s="26" t="s">
-        <v>433</v>
+        <v>231</v>
       </c>
       <c r="M69" s="26" t="s">
         <v>57</v>
@@ -7346,10 +7333,10 @@
         <v>56</v>
       </c>
       <c r="O69" s="26" t="s">
-        <v>466</v>
+        <v>116</v>
       </c>
       <c r="P69" s="26" t="s">
-        <v>467</v>
+        <v>115</v>
       </c>
       <c r="Q69" s="26"/>
       <c r="R69" s="26"/>
@@ -7357,28 +7344,28 @@
     </row>
     <row r="70" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
-        <v>431</v>
+        <v>519</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C70" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E70" s="26" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G70" s="26" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H70" s="26" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="I70" s="39">
         <v>4</v>
@@ -7388,7 +7375,7 @@
       </c>
       <c r="K70" s="39"/>
       <c r="L70" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M70" s="26" t="s">
         <v>57</v>
@@ -7397,27 +7384,27 @@
         <v>56</v>
       </c>
       <c r="O70" s="26" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="P70" s="26" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="Q70" s="26"/>
       <c r="R70" s="26"/>
-      <c r="S70" s="30"/>
+      <c r="S70" s="26"/>
     </row>
     <row r="71" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C71" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E71" s="26" t="s">
         <v>528</v>
@@ -7426,109 +7413,111 @@
         <v>500</v>
       </c>
       <c r="G71" s="26" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H71" s="26" t="s">
-        <v>556</v>
+        <v>522</v>
       </c>
       <c r="I71" s="39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J71" s="39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K71" s="39"/>
       <c r="L71" s="26" t="s">
-        <v>229</v>
+        <v>521</v>
       </c>
       <c r="M71" s="26" t="s">
         <v>57</v>
       </c>
       <c r="N71" s="26" t="s">
-        <v>56</v>
+        <v>522</v>
       </c>
       <c r="O71" s="26" t="s">
-        <v>76</v>
+        <v>523</v>
       </c>
       <c r="P71" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q71" s="26"/>
-      <c r="R71" s="26"/>
-      <c r="S71" s="26"/>
+        <v>524</v>
+      </c>
+      <c r="Q71" s="28"/>
+      <c r="R71" s="28"/>
+      <c r="S71" s="29"/>
     </row>
     <row r="72" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
-        <v>522</v>
+        <v>303</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C72" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>599</v>
-      </c>
-      <c r="E72" s="26" t="s">
-        <v>530</v>
-      </c>
-      <c r="F72" s="26" t="s">
-        <v>501</v>
-      </c>
-      <c r="G72" s="26" t="s">
-        <v>565</v>
-      </c>
-      <c r="H72" s="26" t="s">
-        <v>524</v>
-      </c>
-      <c r="I72" s="39">
-        <v>5</v>
-      </c>
-      <c r="J72" s="39">
-        <v>5</v>
-      </c>
-      <c r="K72" s="39"/>
-      <c r="L72" s="26" t="s">
-        <v>523</v>
-      </c>
-      <c r="M72" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="N72" s="26" t="s">
-        <v>524</v>
-      </c>
-      <c r="O72" s="26" t="s">
-        <v>525</v>
-      </c>
-      <c r="P72" s="26" t="s">
-        <v>526</v>
-      </c>
-      <c r="Q72" s="28"/>
-      <c r="R72" s="28"/>
-      <c r="S72" s="29"/>
+        <v>597</v>
+      </c>
+      <c r="E72" s="27" t="s">
+        <v>531</v>
+      </c>
+      <c r="F72" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="G72" s="23" t="s">
+        <v>580</v>
+      </c>
+      <c r="H72" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="I72" s="40">
+        <v>6.1</v>
+      </c>
+      <c r="J72" s="40">
+        <v>6</v>
+      </c>
+      <c r="K72" s="40">
+        <v>1</v>
+      </c>
+      <c r="L72" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="M72" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="N72" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="O72" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="P72" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q72" s="23"/>
+      <c r="R72" s="23"/>
+      <c r="S72" s="23"/>
     </row>
     <row r="73" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="B73" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C73" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E73" s="27" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F73" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G73" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H73" s="27" t="s">
         <v>59</v>
@@ -7543,7 +7532,7 @@
         <v>1</v>
       </c>
       <c r="L73" s="23" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="M73" s="23" t="s">
         <v>53</v>
@@ -7552,10 +7541,10 @@
         <v>59</v>
       </c>
       <c r="O73" s="23" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="P73" s="23" t="s">
-        <v>52</v>
+        <v>382</v>
       </c>
       <c r="Q73" s="23"/>
       <c r="R73" s="23"/>
@@ -7563,40 +7552,40 @@
     </row>
     <row r="74" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
-        <v>311</v>
+        <v>348</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C74" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>600</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>533</v>
+        <v>597</v>
+      </c>
+      <c r="E74" s="23" t="s">
+        <v>531</v>
       </c>
       <c r="F74" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G74" s="23" t="s">
-        <v>582</v>
-      </c>
-      <c r="H74" s="27" t="s">
+        <v>580</v>
+      </c>
+      <c r="H74" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="I74" s="40">
+      <c r="I74" s="34">
         <v>6.1</v>
       </c>
       <c r="J74" s="40">
         <v>6</v>
       </c>
-      <c r="K74" s="40">
+      <c r="K74" s="34">
         <v>1</v>
       </c>
       <c r="L74" s="23" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="M74" s="23" t="s">
         <v>53</v>
@@ -7605,36 +7594,38 @@
         <v>59</v>
       </c>
       <c r="O74" s="23" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="P74" s="23" t="s">
-        <v>383</v>
+        <v>300</v>
       </c>
       <c r="Q74" s="23"/>
       <c r="R74" s="23"/>
-      <c r="S74" s="23"/>
+      <c r="S74" s="23" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="75" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>349</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C75" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G75" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H75" s="23" t="s">
         <v>59</v>
@@ -7671,25 +7662,25 @@
     </row>
     <row r="76" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="B76" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C76" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G76" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H76" s="23" t="s">
         <v>59</v>
@@ -7704,7 +7695,7 @@
         <v>1</v>
       </c>
       <c r="L76" s="23" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="M76" s="23" t="s">
         <v>53</v>
@@ -7713,38 +7704,36 @@
         <v>59</v>
       </c>
       <c r="O76" s="23" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="P76" s="23" t="s">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="Q76" s="23"/>
       <c r="R76" s="23"/>
-      <c r="S76" s="23" t="s">
-        <v>312</v>
-      </c>
+      <c r="S76" s="23"/>
     </row>
     <row r="77" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B77" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C77" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G77" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H77" s="23" t="s">
         <v>59</v>
@@ -7771,7 +7760,7 @@
         <v>58</v>
       </c>
       <c r="P77" s="23" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q77" s="23"/>
       <c r="R77" s="23"/>
@@ -7779,25 +7768,25 @@
     </row>
     <row r="78" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C78" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G78" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H78" s="23" t="s">
         <v>59</v>
@@ -7824,7 +7813,7 @@
         <v>58</v>
       </c>
       <c r="P78" s="23" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q78" s="23"/>
       <c r="R78" s="23"/>
@@ -7832,25 +7821,25 @@
     </row>
     <row r="79" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
-        <v>282</v>
+        <v>324</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C79" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G79" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H79" s="23" t="s">
         <v>59</v>
@@ -7865,7 +7854,7 @@
         <v>1</v>
       </c>
       <c r="L79" s="23" t="s">
-        <v>286</v>
+        <v>236</v>
       </c>
       <c r="M79" s="23" t="s">
         <v>53</v>
@@ -7877,44 +7866,46 @@
         <v>58</v>
       </c>
       <c r="P79" s="23" t="s">
-        <v>381</v>
+        <v>52</v>
       </c>
       <c r="Q79" s="23"/>
       <c r="R79" s="23"/>
-      <c r="S79" s="23"/>
+      <c r="S79" s="23" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="80" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="B80" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C80" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>600</v>
-      </c>
-      <c r="E80" s="23" t="s">
-        <v>533</v>
+        <v>597</v>
+      </c>
+      <c r="E80" s="27" t="s">
+        <v>531</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G80" s="23" t="s">
-        <v>582</v>
-      </c>
-      <c r="H80" s="23" t="s">
+        <v>580</v>
+      </c>
+      <c r="H80" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="I80" s="34">
+      <c r="I80" s="40">
         <v>6.1</v>
       </c>
       <c r="J80" s="40">
         <v>6</v>
       </c>
-      <c r="K80" s="34">
+      <c r="K80" s="40">
         <v>1</v>
       </c>
       <c r="L80" s="23" t="s">
@@ -7940,25 +7931,25 @@
     </row>
     <row r="81" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C81" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G81" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H81" s="27" t="s">
         <v>59</v>
@@ -7973,7 +7964,7 @@
         <v>1</v>
       </c>
       <c r="L81" s="23" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="M81" s="23" t="s">
         <v>53</v>
@@ -7982,10 +7973,10 @@
         <v>59</v>
       </c>
       <c r="O81" s="23" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="P81" s="23" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="Q81" s="23"/>
       <c r="R81" s="23"/>
@@ -7998,22 +7989,22 @@
         <v>336</v>
       </c>
       <c r="B82" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C82" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G82" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H82" s="27" t="s">
         <v>59</v>
@@ -8050,40 +8041,40 @@
     </row>
     <row r="83" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
-        <v>337</v>
+        <v>511</v>
       </c>
       <c r="B83" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C83" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>600</v>
-      </c>
-      <c r="E83" s="27" t="s">
-        <v>533</v>
+        <v>597</v>
+      </c>
+      <c r="E83" s="23" t="s">
+        <v>531</v>
       </c>
       <c r="F83" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G83" s="23" t="s">
-        <v>582</v>
-      </c>
-      <c r="H83" s="27" t="s">
+        <v>580</v>
+      </c>
+      <c r="H83" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="I83" s="40">
+      <c r="I83" s="34">
         <v>6.1</v>
       </c>
       <c r="J83" s="40">
         <v>6</v>
       </c>
-      <c r="K83" s="40">
+      <c r="K83" s="34">
         <v>1</v>
       </c>
       <c r="L83" s="23" t="s">
-        <v>222</v>
+        <v>518</v>
       </c>
       <c r="M83" s="23" t="s">
         <v>53</v>
@@ -8092,38 +8083,36 @@
         <v>59</v>
       </c>
       <c r="O83" s="23" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="P83" s="23" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="Q83" s="23"/>
       <c r="R83" s="23"/>
-      <c r="S83" s="23" t="s">
-        <v>312</v>
-      </c>
+      <c r="S83" s="23"/>
     </row>
     <row r="84" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B84" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C84" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F84" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G84" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H84" s="23" t="s">
         <v>59</v>
@@ -8138,7 +8127,7 @@
         <v>1</v>
       </c>
       <c r="L84" s="23" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="M84" s="23" t="s">
         <v>53</v>
@@ -8158,25 +8147,25 @@
     </row>
     <row r="85" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C85" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D85" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E85" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F85" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G85" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H85" s="23" t="s">
         <v>59</v>
@@ -8191,7 +8180,7 @@
         <v>1</v>
       </c>
       <c r="L85" s="23" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="M85" s="23" t="s">
         <v>53</v>
@@ -8211,25 +8200,25 @@
     </row>
     <row r="86" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B86" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C86" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E86" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F86" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G86" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H86" s="23" t="s">
         <v>59</v>
@@ -8244,7 +8233,7 @@
         <v>1</v>
       </c>
       <c r="L86" s="23" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="M86" s="23" t="s">
         <v>53</v>
@@ -8264,25 +8253,25 @@
     </row>
     <row r="87" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C87" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E87" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F87" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G87" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H87" s="23" t="s">
         <v>59</v>
@@ -8297,7 +8286,7 @@
         <v>1</v>
       </c>
       <c r="L87" s="23" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="M87" s="23" t="s">
         <v>53</v>
@@ -8317,25 +8306,25 @@
     </row>
     <row r="88" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B88" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C88" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E88" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F88" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G88" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H88" s="23" t="s">
         <v>59</v>
@@ -8350,7 +8339,7 @@
         <v>1</v>
       </c>
       <c r="L88" s="23" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="M88" s="23" t="s">
         <v>53</v>
@@ -8370,25 +8359,25 @@
     </row>
     <row r="89" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C89" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D89" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E89" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F89" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G89" s="23" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H89" s="23" t="s">
         <v>59</v>
@@ -8403,7 +8392,7 @@
         <v>1</v>
       </c>
       <c r="L89" s="23" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="M89" s="23" t="s">
         <v>53</v>
@@ -8423,84 +8412,86 @@
     </row>
     <row r="90" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
-        <v>519</v>
+        <v>207</v>
       </c>
       <c r="B90" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C90" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E90" s="23" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F90" s="23" t="s">
-        <v>500</v>
-      </c>
-      <c r="G90" s="23" t="s">
-        <v>582</v>
-      </c>
-      <c r="H90" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="G90" s="31" t="s">
+        <v>580</v>
+      </c>
+      <c r="H90" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="I90" s="34">
+      <c r="I90" s="41">
         <v>6.1</v>
       </c>
       <c r="J90" s="40">
         <v>6</v>
       </c>
       <c r="K90" s="34">
-        <v>1</v>
-      </c>
-      <c r="L90" s="23" t="s">
-        <v>520</v>
-      </c>
-      <c r="M90" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="L90" s="32" t="s">
+        <v>237</v>
+      </c>
+      <c r="M90" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="N90" s="23" t="s">
+      <c r="N90" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="O90" s="23" t="s">
+      <c r="O90" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="P90" s="23" t="s">
+      <c r="P90" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="Q90" s="23"/>
-      <c r="R90" s="23"/>
-      <c r="S90" s="23"/>
+      <c r="Q90" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="R90" s="33"/>
+      <c r="S90" s="32"/>
     </row>
     <row r="91" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="B91" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C91" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E91" s="23" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F91" s="23" t="s">
         <v>500</v>
       </c>
-      <c r="G91" s="31" t="s">
-        <v>582</v>
-      </c>
-      <c r="H91" s="32" t="s">
+      <c r="G91" s="23" t="s">
+        <v>581</v>
+      </c>
+      <c r="H91" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="I91" s="41">
-        <v>6.1</v>
+      <c r="I91" s="34">
+        <v>6.2</v>
       </c>
       <c r="J91" s="40">
         <v>6</v>
@@ -8508,48 +8499,48 @@
       <c r="K91" s="34">
         <v>2</v>
       </c>
-      <c r="L91" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="M91" s="32" t="s">
+      <c r="L91" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="M91" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="N91" s="32" t="s">
+      <c r="N91" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="O91" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="P91" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q91" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="R91" s="33"/>
-      <c r="S91" s="32"/>
+      <c r="O91" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="P91" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q91" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="R91" s="23"/>
+      <c r="S91" s="23"/>
     </row>
     <row r="92" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="8" t="s">
-        <v>175</v>
+        <v>354</v>
       </c>
       <c r="B92" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C92" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E92" s="23" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F92" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G92" s="23" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H92" s="23" t="s">
         <v>59</v>
@@ -8578,33 +8569,33 @@
       <c r="P92" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="Q92" s="23" t="s">
-        <v>46</v>
-      </c>
+      <c r="Q92" s="23"/>
       <c r="R92" s="23"/>
-      <c r="S92" s="23"/>
+      <c r="S92" s="23" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="93" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="8" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C93" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E93" s="23" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F93" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G93" s="23" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H93" s="23" t="s">
         <v>59</v>
@@ -8619,7 +8610,7 @@
         <v>2</v>
       </c>
       <c r="L93" s="23" t="s">
-        <v>221</v>
+        <v>309</v>
       </c>
       <c r="M93" s="23" t="s">
         <v>53</v>
@@ -8628,151 +8619,147 @@
         <v>59</v>
       </c>
       <c r="O93" s="23" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="P93" s="23" t="s">
-        <v>117</v>
+        <v>382</v>
       </c>
       <c r="Q93" s="23"/>
       <c r="R93" s="23"/>
-      <c r="S93" s="23" t="s">
-        <v>312</v>
+      <c r="S93" s="23">
+        <v>21278349</v>
       </c>
     </row>
     <row r="94" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="8" t="s">
-        <v>315</v>
+        <v>176</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C94" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D94" s="23" t="s">
-        <v>601</v>
-      </c>
-      <c r="E94" s="23" t="s">
-        <v>534</v>
-      </c>
-      <c r="F94" s="23" t="s">
-        <v>501</v>
-      </c>
-      <c r="G94" s="23" t="s">
-        <v>583</v>
-      </c>
-      <c r="H94" s="23" t="s">
+        <v>598</v>
+      </c>
+      <c r="E94" s="26" t="s">
+        <v>532</v>
+      </c>
+      <c r="F94" s="26" t="s">
+        <v>500</v>
+      </c>
+      <c r="G94" s="26" t="s">
+        <v>581</v>
+      </c>
+      <c r="H94" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="I94" s="34">
+      <c r="I94" s="39">
         <v>6.2</v>
       </c>
       <c r="J94" s="40">
         <v>6</v>
       </c>
-      <c r="K94" s="34">
+      <c r="K94" s="39">
         <v>2</v>
       </c>
-      <c r="L94" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="M94" s="23" t="s">
+      <c r="L94" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="M94" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="N94" s="23" t="s">
+      <c r="N94" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="O94" s="23" t="s">
+      <c r="O94" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="P94" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q94" s="23"/>
-      <c r="R94" s="23"/>
-      <c r="S94" s="23">
-        <v>21278349</v>
-      </c>
+      <c r="P94" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q94" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="R94" s="26"/>
+      <c r="S94" s="26"/>
     </row>
     <row r="95" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
-        <v>176</v>
+        <v>274</v>
       </c>
       <c r="B95" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C95" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D95" s="23" t="s">
-        <v>601</v>
-      </c>
-      <c r="E95" s="26" t="s">
-        <v>534</v>
-      </c>
-      <c r="F95" s="26" t="s">
-        <v>501</v>
-      </c>
-      <c r="G95" s="26" t="s">
-        <v>583</v>
-      </c>
-      <c r="H95" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="I95" s="39">
-        <v>6.2</v>
-      </c>
-      <c r="J95" s="40">
-        <v>6</v>
-      </c>
-      <c r="K95" s="39">
-        <v>2</v>
-      </c>
-      <c r="L95" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="M95" s="26" t="s">
+        <v>599</v>
+      </c>
+      <c r="E95" s="23" t="s">
+        <v>538</v>
+      </c>
+      <c r="F95" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="G95" s="23" t="s">
+        <v>564</v>
+      </c>
+      <c r="H95" s="23" t="s">
+        <v>555</v>
+      </c>
+      <c r="I95" s="34">
+        <v>7</v>
+      </c>
+      <c r="J95" s="34">
+        <v>7</v>
+      </c>
+      <c r="K95" s="34"/>
+      <c r="L95" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="M95" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="N95" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="O95" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="P95" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q95" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="R95" s="26"/>
-      <c r="S95" s="26"/>
+      <c r="N95" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="O95" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="P95" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q95" s="23"/>
+      <c r="R95" s="23"/>
+      <c r="S95" s="23"/>
     </row>
     <row r="96" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
-        <v>274</v>
+        <v>194</v>
       </c>
       <c r="B96" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C96" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D96" s="23" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E96" s="23" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F96" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G96" s="23" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H96" s="23" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I96" s="34">
         <v>7</v>
@@ -8782,7 +8769,7 @@
       </c>
       <c r="K96" s="34"/>
       <c r="L96" s="23" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="M96" s="23" t="s">
         <v>53</v>
@@ -8791,39 +8778,41 @@
         <v>72</v>
       </c>
       <c r="O96" s="23" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="P96" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q96" s="23"/>
+        <v>104</v>
+      </c>
+      <c r="Q96" s="23" t="s">
+        <v>18</v>
+      </c>
       <c r="R96" s="23"/>
       <c r="S96" s="23"/>
     </row>
     <row r="97" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="8" t="s">
-        <v>194</v>
+        <v>329</v>
       </c>
       <c r="B97" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C97" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E97" s="23" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F97" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G97" s="23" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H97" s="23" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I97" s="34">
         <v>7</v>
@@ -8833,7 +8822,7 @@
       </c>
       <c r="K97" s="34"/>
       <c r="L97" s="23" t="s">
-        <v>242</v>
+        <v>363</v>
       </c>
       <c r="M97" s="23" t="s">
         <v>53</v>
@@ -8842,41 +8831,41 @@
         <v>72</v>
       </c>
       <c r="O97" s="23" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P97" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q97" s="23" t="s">
-        <v>18</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="Q97" s="23"/>
       <c r="R97" s="23"/>
-      <c r="S97" s="23"/>
+      <c r="S97" s="23" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="98" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="8" t="s">
-        <v>330</v>
+        <v>195</v>
       </c>
       <c r="B98" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C98" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D98" s="23" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F98" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G98" s="23" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H98" s="23" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I98" s="34">
         <v>7</v>
@@ -8886,7 +8875,7 @@
       </c>
       <c r="K98" s="34"/>
       <c r="L98" s="23" t="s">
-        <v>364</v>
+        <v>243</v>
       </c>
       <c r="M98" s="23" t="s">
         <v>53</v>
@@ -8900,36 +8889,36 @@
       <c r="P98" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="Q98" s="23"/>
+      <c r="Q98" s="23" t="s">
+        <v>21</v>
+      </c>
       <c r="R98" s="23"/>
-      <c r="S98" s="23" t="s">
-        <v>312</v>
-      </c>
+      <c r="S98" s="23"/>
     </row>
     <row r="99" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B99" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C99" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D99" s="23" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E99" s="23" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F99" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G99" s="23" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H99" s="23" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I99" s="34">
         <v>7</v>
@@ -8939,50 +8928,50 @@
       </c>
       <c r="K99" s="34"/>
       <c r="L99" s="23" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="M99" s="23" t="s">
         <v>53</v>
       </c>
       <c r="N99" s="23" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="O99" s="23" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="P99" s="23" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="Q99" s="23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R99" s="23"/>
       <c r="S99" s="23"/>
     </row>
     <row r="100" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="8" t="s">
-        <v>190</v>
+        <v>279</v>
       </c>
       <c r="B100" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C100" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D100" s="23" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E100" s="23" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F100" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G100" s="23" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H100" s="23" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I100" s="34">
         <v>7</v>
@@ -9006,36 +8995,34 @@
       <c r="P100" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="Q100" s="23" t="s">
-        <v>19</v>
-      </c>
+      <c r="Q100" s="23"/>
       <c r="R100" s="23"/>
       <c r="S100" s="23"/>
     </row>
     <row r="101" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
-        <v>279</v>
+        <v>340</v>
       </c>
       <c r="B101" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C101" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D101" s="23" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E101" s="23" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F101" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G101" s="23" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H101" s="23" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I101" s="34">
         <v>7</v>
@@ -9045,48 +9032,50 @@
       </c>
       <c r="K101" s="34"/>
       <c r="L101" s="23" t="s">
-        <v>220</v>
+        <v>288</v>
       </c>
       <c r="M101" s="23" t="s">
         <v>53</v>
       </c>
       <c r="N101" s="23" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="O101" s="23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="P101" s="23" t="s">
-        <v>106</v>
+        <v>387</v>
       </c>
       <c r="Q101" s="23"/>
       <c r="R101" s="23"/>
-      <c r="S101" s="23"/>
+      <c r="S101" s="23" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="102" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="8" t="s">
-        <v>341</v>
+        <v>283</v>
       </c>
       <c r="B102" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C102" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D102" s="23" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E102" s="23" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F102" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G102" s="23" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H102" s="23" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I102" s="34">
         <v>7</v>
@@ -9108,89 +9097,89 @@
         <v>105</v>
       </c>
       <c r="P102" s="23" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q102" s="23"/>
       <c r="R102" s="23"/>
-      <c r="S102" s="23" t="s">
-        <v>312</v>
-      </c>
+      <c r="S102" s="23"/>
     </row>
     <row r="103" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
-        <v>283</v>
+        <v>206</v>
       </c>
       <c r="B103" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C103" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D103" s="23" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E103" s="23" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F103" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G103" s="23" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H103" s="23" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I103" s="34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J103" s="34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K103" s="34"/>
       <c r="L103" s="23" t="s">
-        <v>288</v>
+        <v>225</v>
       </c>
       <c r="M103" s="23" t="s">
         <v>53</v>
       </c>
       <c r="N103" s="23" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="O103" s="23" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="P103" s="23" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q103" s="23"/>
+        <v>88</v>
+      </c>
+      <c r="Q103" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="R103" s="23"/>
       <c r="S103" s="23"/>
     </row>
     <row r="104" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
-        <v>206</v>
+        <v>284</v>
       </c>
       <c r="B104" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C104" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E104" s="23" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F104" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G104" s="23" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H104" s="23" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="I104" s="34">
         <v>8</v>
@@ -9214,87 +9203,87 @@
       <c r="P104" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="Q104" s="23" t="s">
-        <v>23</v>
-      </c>
+      <c r="Q104" s="23"/>
       <c r="R104" s="23"/>
       <c r="S104" s="23"/>
     </row>
     <row r="105" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
-        <v>284</v>
+        <v>333</v>
       </c>
       <c r="B105" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C105" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D105" s="23" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E105" s="23" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="F105" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G105" s="23" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H105" s="23" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="I105" s="34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J105" s="34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K105" s="34"/>
       <c r="L105" s="23" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="M105" s="23" t="s">
         <v>53</v>
       </c>
       <c r="N105" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O105" s="23" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="P105" s="23" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="Q105" s="23"/>
       <c r="R105" s="23"/>
-      <c r="S105" s="23"/>
+      <c r="S105" s="23" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="106" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
-        <v>334</v>
+        <v>193</v>
       </c>
       <c r="B106" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C106" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D106" s="23" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E106" s="23" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F106" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G106" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H106" s="23" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="I106" s="34">
         <v>9</v>
@@ -9304,7 +9293,7 @@
       </c>
       <c r="K106" s="34"/>
       <c r="L106" s="23" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="M106" s="23" t="s">
         <v>53</v>
@@ -9313,41 +9302,41 @@
         <v>87</v>
       </c>
       <c r="O106" s="23" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="P106" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q106" s="23"/>
+        <v>85</v>
+      </c>
+      <c r="Q106" s="23" t="s">
+        <v>13</v>
+      </c>
       <c r="R106" s="23"/>
-      <c r="S106" s="23" t="s">
-        <v>312</v>
-      </c>
+      <c r="S106" s="23"/>
     </row>
     <row r="107" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
-        <v>193</v>
+        <v>318</v>
       </c>
       <c r="B107" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C107" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E107" s="23" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F107" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G107" s="23" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H107" s="23" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="I107" s="34">
         <v>9</v>
@@ -9357,7 +9346,7 @@
       </c>
       <c r="K107" s="34"/>
       <c r="L107" s="23" t="s">
-        <v>223</v>
+        <v>152</v>
       </c>
       <c r="M107" s="23" t="s">
         <v>53</v>
@@ -9366,92 +9355,94 @@
         <v>87</v>
       </c>
       <c r="O107" s="23" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="P107" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q107" s="23" t="s">
-        <v>13</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="Q107" s="23"/>
       <c r="R107" s="23"/>
       <c r="S107" s="23"/>
     </row>
     <row r="108" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
-        <v>318</v>
+        <v>210</v>
       </c>
       <c r="B108" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C108" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D108" s="23" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E108" s="23" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="F108" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G108" s="23" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H108" s="23" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I108" s="34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J108" s="34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K108" s="34"/>
       <c r="L108" s="23" t="s">
-        <v>152</v>
+        <v>219</v>
       </c>
       <c r="M108" s="23" t="s">
         <v>53</v>
       </c>
       <c r="N108" s="23" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="O108" s="23" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="P108" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q108" s="23"/>
-      <c r="R108" s="23"/>
+        <v>109</v>
+      </c>
+      <c r="Q108" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="R108" s="23" t="s">
+        <v>142</v>
+      </c>
       <c r="S108" s="23"/>
     </row>
     <row r="109" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="B109" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C109" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D109" s="23" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E109" s="23" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F109" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G109" s="23" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H109" s="23" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I109" s="34">
         <v>10</v>
@@ -9461,7 +9452,7 @@
       </c>
       <c r="K109" s="34"/>
       <c r="L109" s="23" t="s">
-        <v>219</v>
+        <v>355</v>
       </c>
       <c r="M109" s="23" t="s">
         <v>53</v>
@@ -9470,43 +9461,39 @@
         <v>111</v>
       </c>
       <c r="O109" s="23" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="P109" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q109" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="R109" s="23" t="s">
-        <v>142</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Q109" s="23"/>
+      <c r="R109" s="23"/>
       <c r="S109" s="23"/>
     </row>
     <row r="110" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
-        <v>316</v>
+        <v>454</v>
       </c>
       <c r="B110" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C110" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D110" s="23" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E110" s="23" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F110" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G110" s="23" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H110" s="23" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I110" s="34">
         <v>10</v>
@@ -9516,7 +9503,7 @@
       </c>
       <c r="K110" s="34"/>
       <c r="L110" s="23" t="s">
-        <v>356</v>
+        <v>461</v>
       </c>
       <c r="M110" s="23" t="s">
         <v>53</v>
@@ -9525,10 +9512,10 @@
         <v>111</v>
       </c>
       <c r="O110" s="23" t="s">
-        <v>156</v>
+        <v>378</v>
       </c>
       <c r="P110" s="23" t="s">
-        <v>157</v>
+        <v>478</v>
       </c>
       <c r="Q110" s="23"/>
       <c r="R110" s="23"/>
@@ -9536,28 +9523,28 @@
     </row>
     <row r="111" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B111" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C111" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D111" s="23" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E111" s="23" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F111" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G111" s="23" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H111" s="23" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I111" s="34">
         <v>10</v>
@@ -9567,7 +9554,7 @@
       </c>
       <c r="K111" s="34"/>
       <c r="L111" s="23" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="M111" s="23" t="s">
         <v>53</v>
@@ -9576,10 +9563,10 @@
         <v>111</v>
       </c>
       <c r="O111" s="23" t="s">
-        <v>379</v>
+        <v>475</v>
       </c>
       <c r="P111" s="23" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="Q111" s="23"/>
       <c r="R111" s="23"/>
@@ -9587,28 +9574,28 @@
     </row>
     <row r="112" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B112" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C112" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D112" s="23" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E112" s="23" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F112" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G112" s="23" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H112" s="23" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I112" s="34">
         <v>10</v>
@@ -9618,7 +9605,7 @@
       </c>
       <c r="K112" s="34"/>
       <c r="L112" s="23" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M112" s="23" t="s">
         <v>53</v>
@@ -9627,10 +9614,10 @@
         <v>111</v>
       </c>
       <c r="O112" s="23" t="s">
-        <v>476</v>
+        <v>378</v>
       </c>
       <c r="P112" s="23" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Q112" s="23"/>
       <c r="R112" s="23"/>
@@ -9638,38 +9625,38 @@
     </row>
     <row r="113" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
-        <v>456</v>
+        <v>203</v>
       </c>
       <c r="B113" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C113" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D113" s="23" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E113" s="23" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F113" s="23" t="s">
         <v>500</v>
       </c>
       <c r="G113" s="23" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H113" s="23" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I113" s="34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J113" s="34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K113" s="34"/>
       <c r="L113" s="23" t="s">
-        <v>463</v>
+        <v>219</v>
       </c>
       <c r="M113" s="23" t="s">
         <v>53</v>
@@ -9678,39 +9665,43 @@
         <v>111</v>
       </c>
       <c r="O113" s="23" t="s">
-        <v>379</v>
+        <v>110</v>
       </c>
       <c r="P113" s="23" t="s">
-        <v>480</v>
-      </c>
-      <c r="Q113" s="23"/>
-      <c r="R113" s="23"/>
+        <v>109</v>
+      </c>
+      <c r="Q113" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="R113" s="23" t="s">
+        <v>142</v>
+      </c>
       <c r="S113" s="23"/>
     </row>
     <row r="114" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
-        <v>203</v>
+        <v>4</v>
       </c>
       <c r="B114" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C114" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D114" s="23" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F114" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G114" s="23" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H114" s="23" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I114" s="34">
         <v>11</v>
@@ -9720,7 +9711,7 @@
       </c>
       <c r="K114" s="34"/>
       <c r="L114" s="23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M114" s="23" t="s">
         <v>53</v>
@@ -9729,43 +9720,41 @@
         <v>111</v>
       </c>
       <c r="O114" s="23" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="P114" s="23" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="Q114" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="R114" s="23" t="s">
-        <v>142</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="R114" s="23"/>
       <c r="S114" s="23"/>
     </row>
     <row r="115" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
-        <v>4</v>
+        <v>308</v>
       </c>
       <c r="B115" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C115" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D115" s="23" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F115" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G115" s="23" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H115" s="23" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I115" s="34">
         <v>11</v>
@@ -9775,7 +9764,7 @@
       </c>
       <c r="K115" s="34"/>
       <c r="L115" s="23" t="s">
-        <v>218</v>
+        <v>307</v>
       </c>
       <c r="M115" s="23" t="s">
         <v>53</v>
@@ -9784,41 +9773,39 @@
         <v>111</v>
       </c>
       <c r="O115" s="23" t="s">
-        <v>128</v>
+        <v>383</v>
       </c>
       <c r="P115" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q115" s="23" t="s">
-        <v>4</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="Q115" s="23"/>
       <c r="R115" s="23"/>
       <c r="S115" s="23"/>
     </row>
     <row r="116" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="B116" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C116" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D116" s="23" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>536</v>
-      </c>
-      <c r="F116" s="23" t="s">
-        <v>501</v>
-      </c>
-      <c r="G116" s="23" t="s">
-        <v>570</v>
+        <v>534</v>
+      </c>
+      <c r="F116" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="G116" s="27" t="s">
+        <v>568</v>
       </c>
       <c r="H116" s="23" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I116" s="34">
         <v>11</v>
@@ -9828,7 +9815,7 @@
       </c>
       <c r="K116" s="34"/>
       <c r="L116" s="23" t="s">
-        <v>307</v>
+        <v>218</v>
       </c>
       <c r="M116" s="23" t="s">
         <v>53</v>
@@ -9837,10 +9824,10 @@
         <v>111</v>
       </c>
       <c r="O116" s="23" t="s">
-        <v>384</v>
+        <v>128</v>
       </c>
       <c r="P116" s="23" t="s">
-        <v>385</v>
+        <v>127</v>
       </c>
       <c r="Q116" s="23"/>
       <c r="R116" s="23"/>
@@ -9848,185 +9835,185 @@
     </row>
     <row r="117" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
-        <v>291</v>
+        <v>180</v>
       </c>
       <c r="B117" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C117" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D117" s="23" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E117" s="23" t="s">
-        <v>536</v>
-      </c>
-      <c r="F117" s="27" t="s">
-        <v>501</v>
-      </c>
-      <c r="G117" s="27" t="s">
-        <v>570</v>
+        <v>504</v>
+      </c>
+      <c r="F117" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="G117" s="23" t="s">
+        <v>569</v>
       </c>
       <c r="H117" s="23" t="s">
-        <v>560</v>
+        <v>124</v>
       </c>
       <c r="I117" s="34">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J117" s="34">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K117" s="34"/>
       <c r="L117" s="23" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="M117" s="23" t="s">
         <v>53</v>
       </c>
       <c r="N117" s="23" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="O117" s="23" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P117" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q117" s="23"/>
+        <v>124</v>
+      </c>
+      <c r="Q117" s="23" t="s">
+        <v>26</v>
+      </c>
       <c r="R117" s="23"/>
       <c r="S117" s="23"/>
     </row>
     <row r="118" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="B118" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C118" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D118" s="23" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E118" s="23" t="s">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="F118" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G118" s="23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H118" s="23" t="s">
-        <v>124</v>
+        <v>556</v>
       </c>
       <c r="I118" s="34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J118" s="34">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K118" s="34"/>
       <c r="L118" s="23" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M118" s="23" t="s">
         <v>53</v>
       </c>
       <c r="N118" s="23" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="O118" s="23" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="P118" s="23" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="Q118" s="23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="R118" s="23"/>
       <c r="S118" s="23"/>
     </row>
     <row r="119" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
-        <v>205</v>
+        <v>317</v>
       </c>
       <c r="B119" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C119" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D119" s="23" t="s">
-        <v>608</v>
-      </c>
-      <c r="E119" s="23" t="s">
-        <v>532</v>
+        <v>606</v>
+      </c>
+      <c r="E119" s="24" t="s">
+        <v>506</v>
       </c>
       <c r="F119" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G119" s="23" t="s">
-        <v>572</v>
-      </c>
-      <c r="H119" s="23" t="s">
-        <v>558</v>
-      </c>
-      <c r="I119" s="34">
-        <v>13</v>
+        <v>571</v>
+      </c>
+      <c r="H119" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="I119" s="42">
+        <v>14</v>
       </c>
       <c r="J119" s="34">
-        <v>13</v>
-      </c>
-      <c r="K119" s="34"/>
-      <c r="L119" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="M119" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="K119" s="42"/>
+      <c r="L119" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="M119" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="N119" s="23" t="s">
+      <c r="N119" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="O119" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="P119" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q119" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="R119" s="23"/>
-      <c r="S119" s="23"/>
+      <c r="O119" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="P119" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q119" s="25"/>
+      <c r="R119" s="25"/>
+      <c r="S119" s="24"/>
     </row>
     <row r="120" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C120" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D120" s="23" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E120" s="24" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F120" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G120" s="23" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H120" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I120" s="42">
         <v>14</v>
@@ -10036,7 +10023,7 @@
       </c>
       <c r="K120" s="42"/>
       <c r="L120" s="24" t="s">
-        <v>357</v>
+        <v>304</v>
       </c>
       <c r="M120" s="24" t="s">
         <v>53</v>
@@ -10045,10 +10032,10 @@
         <v>90</v>
       </c>
       <c r="O120" s="24" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="P120" s="24" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="Q120" s="25"/>
       <c r="R120" s="25"/>
@@ -10056,28 +10043,28 @@
     </row>
     <row r="121" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B121" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C121" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D121" s="23" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E121" s="24" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F121" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G121" s="23" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H121" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I121" s="42">
         <v>14</v>
@@ -10087,48 +10074,50 @@
       </c>
       <c r="K121" s="42"/>
       <c r="L121" s="24" t="s">
-        <v>304</v>
+        <v>358</v>
       </c>
       <c r="M121" s="24" t="s">
         <v>53</v>
       </c>
       <c r="N121" s="24" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="O121" s="24" t="s">
-        <v>89</v>
+        <v>383</v>
       </c>
       <c r="P121" s="24" t="s">
-        <v>88</v>
+        <v>384</v>
       </c>
       <c r="Q121" s="25"/>
       <c r="R121" s="25"/>
-      <c r="S121" s="24"/>
+      <c r="S121" s="24" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="122" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B122" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C122" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D122" s="23" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E122" s="24" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F122" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G122" s="23" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H122" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I122" s="42">
         <v>14</v>
@@ -10138,7 +10127,7 @@
       </c>
       <c r="K122" s="42"/>
       <c r="L122" s="24" t="s">
-        <v>359</v>
+        <v>218</v>
       </c>
       <c r="M122" s="24" t="s">
         <v>53</v>
@@ -10147,10 +10136,10 @@
         <v>111</v>
       </c>
       <c r="O122" s="24" t="s">
-        <v>384</v>
+        <v>128</v>
       </c>
       <c r="P122" s="24" t="s">
-        <v>385</v>
+        <v>127</v>
       </c>
       <c r="Q122" s="25"/>
       <c r="R122" s="25"/>
@@ -10160,28 +10149,28 @@
     </row>
     <row r="123" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
-        <v>313</v>
+        <v>179</v>
       </c>
       <c r="B123" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C123" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D123" s="23" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E123" s="24" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F123" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G123" s="23" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H123" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I123" s="42">
         <v>14</v>
@@ -10191,50 +10180,50 @@
       </c>
       <c r="K123" s="42"/>
       <c r="L123" s="24" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="M123" s="24" t="s">
         <v>53</v>
       </c>
       <c r="N123" s="24" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="O123" s="24" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="P123" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q123" s="25"/>
+        <v>88</v>
+      </c>
+      <c r="Q123" s="25" t="s">
+        <v>25</v>
+      </c>
       <c r="R123" s="25"/>
-      <c r="S123" s="24" t="s">
-        <v>312</v>
-      </c>
+      <c r="S123" s="24"/>
     </row>
     <row r="124" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="B124" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C124" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D124" s="23" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E124" s="24" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F124" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G124" s="23" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H124" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I124" s="42">
         <v>14</v>
@@ -10244,50 +10233,52 @@
       </c>
       <c r="K124" s="42"/>
       <c r="L124" s="24" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="M124" s="24" t="s">
         <v>53</v>
       </c>
       <c r="N124" s="24" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="O124" s="24" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="P124" s="24" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="Q124" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="R124" s="25"/>
+        <v>30</v>
+      </c>
+      <c r="R124" s="25" t="s">
+        <v>142</v>
+      </c>
       <c r="S124" s="24"/>
     </row>
     <row r="125" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="B125" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C125" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D125" s="23" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E125" s="24" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F125" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G125" s="23" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H125" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I125" s="42">
         <v>14</v>
@@ -10297,52 +10288,50 @@
       </c>
       <c r="K125" s="42"/>
       <c r="L125" s="24" t="s">
-        <v>219</v>
+        <v>7</v>
       </c>
       <c r="M125" s="24" t="s">
         <v>53</v>
       </c>
       <c r="N125" s="24" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="O125" s="24" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="P125" s="24" t="s">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="Q125" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="R125" s="25" t="s">
-        <v>142</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="R125" s="25"/>
       <c r="S125" s="24"/>
     </row>
     <row r="126" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="B126" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C126" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D126" s="23" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E126" s="24" t="s">
-        <v>507</v>
-      </c>
-      <c r="F126" s="23" t="s">
-        <v>501</v>
-      </c>
-      <c r="G126" s="23" t="s">
-        <v>573</v>
+        <v>506</v>
+      </c>
+      <c r="F126" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="G126" s="27" t="s">
+        <v>571</v>
       </c>
       <c r="H126" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I126" s="42">
         <v>14</v>
@@ -10352,50 +10341,50 @@
       </c>
       <c r="K126" s="42"/>
       <c r="L126" s="24" t="s">
-        <v>7</v>
+        <v>238</v>
       </c>
       <c r="M126" s="24" t="s">
         <v>53</v>
       </c>
       <c r="N126" s="24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="O126" s="24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P126" s="24" t="s">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="Q126" s="25" t="s">
-        <v>213</v>
+        <v>15</v>
       </c>
       <c r="R126" s="25"/>
       <c r="S126" s="24"/>
     </row>
     <row r="127" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B127" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C127" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D127" s="23" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E127" s="24" t="s">
-        <v>507</v>
-      </c>
-      <c r="F127" s="27" t="s">
-        <v>501</v>
-      </c>
-      <c r="G127" s="27" t="s">
-        <v>573</v>
+        <v>506</v>
+      </c>
+      <c r="F127" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="G127" s="23" t="s">
+        <v>571</v>
       </c>
       <c r="H127" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I127" s="42">
         <v>14</v>
@@ -10405,50 +10394,50 @@
       </c>
       <c r="K127" s="42"/>
       <c r="L127" s="24" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="M127" s="24" t="s">
         <v>53</v>
       </c>
       <c r="N127" s="24" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="O127" s="24" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="P127" s="24" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="Q127" s="25" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="R127" s="25"/>
       <c r="S127" s="24"/>
     </row>
     <row r="128" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
-        <v>181</v>
+        <v>51</v>
       </c>
       <c r="B128" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C128" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D128" s="23" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E128" s="24" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F128" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G128" s="23" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H128" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I128" s="42">
         <v>14</v>
@@ -10458,50 +10447,50 @@
       </c>
       <c r="K128" s="42"/>
       <c r="L128" s="24" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="M128" s="24" t="s">
         <v>53</v>
       </c>
       <c r="N128" s="24" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="O128" s="24" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="P128" s="24" t="s">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="Q128" s="25" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="R128" s="25"/>
       <c r="S128" s="24"/>
     </row>
     <row r="129" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
-        <v>51</v>
+        <v>446</v>
       </c>
       <c r="B129" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C129" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D129" s="23" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E129" s="24" t="s">
-        <v>507</v>
-      </c>
-      <c r="F129" s="23" t="s">
-        <v>501</v>
-      </c>
-      <c r="G129" s="23" t="s">
-        <v>573</v>
+        <v>506</v>
+      </c>
+      <c r="F129" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="G129" s="27" t="s">
+        <v>571</v>
       </c>
       <c r="H129" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I129" s="42">
         <v>14</v>
@@ -10511,156 +10500,154 @@
       </c>
       <c r="K129" s="42"/>
       <c r="L129" s="24" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M129" s="24" t="s">
         <v>53</v>
       </c>
       <c r="N129" s="24" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="O129" s="24" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="P129" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q129" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="R129" s="25"/>
+        <v>70</v>
+      </c>
+      <c r="Q129" s="24"/>
+      <c r="R129" s="24"/>
       <c r="S129" s="24"/>
     </row>
     <row r="130" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
-        <v>447</v>
+        <v>182</v>
       </c>
       <c r="B130" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C130" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D130" s="23" t="s">
-        <v>609</v>
-      </c>
-      <c r="E130" s="24" t="s">
+        <v>607</v>
+      </c>
+      <c r="E130" s="23" t="s">
         <v>507</v>
       </c>
-      <c r="F130" s="27" t="s">
-        <v>501</v>
-      </c>
-      <c r="G130" s="27" t="s">
-        <v>573</v>
-      </c>
-      <c r="H130" s="24" t="s">
-        <v>491</v>
-      </c>
-      <c r="I130" s="42">
-        <v>14</v>
+      <c r="F130" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="G130" s="23" t="s">
+        <v>572</v>
+      </c>
+      <c r="H130" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="I130" s="34">
+        <v>15</v>
       </c>
       <c r="J130" s="34">
-        <v>14</v>
-      </c>
-      <c r="K130" s="42"/>
-      <c r="L130" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="M130" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="N130" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="O130" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="P130" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q130" s="24"/>
-      <c r="R130" s="24"/>
-      <c r="S130" s="24"/>
+        <v>15</v>
+      </c>
+      <c r="K130" s="34"/>
+      <c r="L130" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="M130" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="N130" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="O130" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="P130" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q130" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="R130" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="S130" s="23"/>
     </row>
     <row r="131" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
-        <v>182</v>
+        <v>278</v>
       </c>
       <c r="B131" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C131" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D131" s="23" t="s">
-        <v>610</v>
-      </c>
-      <c r="E131" s="23" t="s">
-        <v>508</v>
+        <v>608</v>
+      </c>
+      <c r="E131" s="24" t="s">
+        <v>542</v>
       </c>
       <c r="F131" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G131" s="23" t="s">
-        <v>574</v>
-      </c>
-      <c r="H131" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="I131" s="34">
-        <v>15</v>
+        <v>573</v>
+      </c>
+      <c r="H131" s="24" t="s">
+        <v>559</v>
+      </c>
+      <c r="I131" s="42">
+        <v>16</v>
       </c>
       <c r="J131" s="34">
-        <v>15</v>
-      </c>
-      <c r="K131" s="34"/>
+        <v>16</v>
+      </c>
+      <c r="K131" s="42"/>
       <c r="L131" s="23" t="s">
-        <v>214</v>
+        <v>285</v>
       </c>
       <c r="M131" s="23" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="N131" s="23" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="O131" s="23" t="s">
-        <v>92</v>
+        <v>374</v>
       </c>
       <c r="P131" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q131" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="R131" s="23" t="s">
-        <v>145</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="Q131" s="23"/>
+      <c r="R131" s="23"/>
       <c r="S131" s="23"/>
     </row>
     <row r="132" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
-        <v>278</v>
+        <v>321</v>
       </c>
       <c r="B132" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C132" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D132" s="23" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E132" s="24" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F132" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G132" s="23" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H132" s="24" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="I132" s="42">
         <v>16</v>
@@ -10670,7 +10657,7 @@
       </c>
       <c r="K132" s="42"/>
       <c r="L132" s="23" t="s">
-        <v>285</v>
+        <v>357</v>
       </c>
       <c r="M132" s="23" t="s">
         <v>84</v>
@@ -10679,10 +10666,10 @@
         <v>72</v>
       </c>
       <c r="O132" s="23" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P132" s="23" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q132" s="23"/>
       <c r="R132" s="23"/>
@@ -10690,129 +10677,133 @@
     </row>
     <row r="133" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
-        <v>321</v>
+        <v>168</v>
       </c>
       <c r="B133" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C133" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D133" s="23" t="s">
-        <v>611</v>
-      </c>
-      <c r="E133" s="24" t="s">
-        <v>544</v>
+        <v>609</v>
+      </c>
+      <c r="E133" s="23" t="s">
+        <v>540</v>
       </c>
       <c r="F133" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G133" s="23" t="s">
-        <v>575</v>
-      </c>
-      <c r="H133" s="24" t="s">
-        <v>561</v>
-      </c>
-      <c r="I133" s="42">
+        <v>574</v>
+      </c>
+      <c r="H133" s="23" t="s">
+        <v>560</v>
+      </c>
+      <c r="I133" s="34">
         <v>16</v>
       </c>
       <c r="J133" s="34">
         <v>16</v>
       </c>
-      <c r="K133" s="42"/>
+      <c r="K133" s="34"/>
       <c r="L133" s="23" t="s">
-        <v>358</v>
+        <v>234</v>
       </c>
       <c r="M133" s="23" t="s">
         <v>84</v>
       </c>
       <c r="N133" s="23" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="O133" s="23" t="s">
-        <v>377</v>
+        <v>113</v>
       </c>
       <c r="P133" s="23" t="s">
-        <v>378</v>
-      </c>
-      <c r="Q133" s="23"/>
+        <v>112</v>
+      </c>
+      <c r="Q133" s="23" t="s">
+        <v>10</v>
+      </c>
       <c r="R133" s="23"/>
       <c r="S133" s="23"/>
     </row>
     <row r="134" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B134" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C134" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D134" s="23" t="s">
-        <v>612</v>
-      </c>
-      <c r="E134" s="23" t="s">
-        <v>542</v>
+        <v>610</v>
+      </c>
+      <c r="E134" s="24" t="s">
+        <v>544</v>
       </c>
       <c r="F134" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G134" s="23" t="s">
-        <v>576</v>
-      </c>
-      <c r="H134" s="23" t="s">
-        <v>562</v>
-      </c>
-      <c r="I134" s="34">
+        <v>575</v>
+      </c>
+      <c r="H134" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="I134" s="42">
         <v>16</v>
       </c>
       <c r="J134" s="34">
         <v>16</v>
       </c>
-      <c r="K134" s="34"/>
+      <c r="K134" s="42"/>
       <c r="L134" s="23" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M134" s="23" t="s">
         <v>84</v>
       </c>
       <c r="N134" s="23" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="O134" s="23" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="P134" s="23" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="Q134" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R134" s="23"/>
+        <v>12</v>
+      </c>
+      <c r="R134" s="23" t="s">
+        <v>140</v>
+      </c>
       <c r="S134" s="23"/>
     </row>
     <row r="135" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="8" t="s">
-        <v>169</v>
+      <c r="A135" s="12" t="s">
+        <v>170</v>
       </c>
       <c r="B135" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C135" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D135" s="23" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E135" s="24" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F135" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G135" s="23" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H135" s="24" t="s">
         <v>123</v>
@@ -10824,108 +10815,104 @@
         <v>16</v>
       </c>
       <c r="K135" s="42"/>
-      <c r="L135" s="23" t="s">
+      <c r="L135" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="M135" s="23" t="s">
+      <c r="M135" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="N135" s="23" t="s">
+      <c r="N135" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="O135" s="23" t="s">
+      <c r="O135" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="P135" s="23" t="s">
+      <c r="P135" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="Q135" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="R135" s="23" t="s">
+      <c r="Q135" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="R135" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="S135" s="23"/>
-    </row>
-    <row r="136" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="12" t="s">
-        <v>170</v>
+      <c r="S135" s="24"/>
+    </row>
+    <row r="136" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="A136" s="8" t="s">
+        <v>319</v>
       </c>
       <c r="B136" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C136" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D136" s="23" t="s">
-        <v>613</v>
-      </c>
-      <c r="E136" s="24" t="s">
-        <v>546</v>
+        <v>611</v>
+      </c>
+      <c r="E136" s="23" t="s">
+        <v>543</v>
       </c>
       <c r="F136" s="23" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G136" s="23" t="s">
-        <v>577</v>
-      </c>
-      <c r="H136" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="I136" s="42">
+        <v>573</v>
+      </c>
+      <c r="H136" s="23" t="s">
+        <v>559</v>
+      </c>
+      <c r="I136" s="34">
         <v>16</v>
       </c>
       <c r="J136" s="34">
         <v>16</v>
       </c>
-      <c r="K136" s="42"/>
-      <c r="L136" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="M136" s="24" t="s">
+      <c r="K136" s="34"/>
+      <c r="L136" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="M136" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="N136" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="O136" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="P136" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q136" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="R136" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="S136" s="24"/>
-    </row>
-    <row r="137" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+      <c r="N136" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="O136" s="23" t="s">
+        <v>376</v>
+      </c>
+      <c r="P136" s="23" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q136" s="23"/>
+      <c r="R136" s="23"/>
+      <c r="S136" s="23"/>
+    </row>
+    <row r="137" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
-        <v>319</v>
+        <v>209</v>
       </c>
       <c r="B137" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C137" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D137" s="23" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E137" s="23" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="F137" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G137" s="23" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H137" s="23" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I137" s="34">
         <v>16</v>
@@ -10935,30 +10922,34 @@
       </c>
       <c r="K137" s="34"/>
       <c r="L137" s="23" t="s">
-        <v>358</v>
+        <v>240</v>
       </c>
       <c r="M137" s="23" t="s">
         <v>84</v>
       </c>
       <c r="N137" s="23" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="O137" s="23" t="s">
-        <v>377</v>
+        <v>82</v>
       </c>
       <c r="P137" s="23" t="s">
-        <v>378</v>
-      </c>
-      <c r="Q137" s="23"/>
-      <c r="R137" s="23"/>
+        <v>81</v>
+      </c>
+      <c r="Q137" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="R137" s="23" t="s">
+        <v>140</v>
+      </c>
       <c r="S137" s="23"/>
     </row>
     <row r="138" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="B138" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C138" s="36" t="s">
         <v>246</v>
@@ -10967,210 +10958,155 @@
         <v>615</v>
       </c>
       <c r="E138" s="23" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="F138" s="23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G138" s="23" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="H138" s="23" t="s">
-        <v>562</v>
-      </c>
-      <c r="I138" s="34">
-        <v>16</v>
-      </c>
-      <c r="J138" s="34">
-        <v>16</v>
+        <v>69</v>
+      </c>
+      <c r="I138" s="34" t="s">
+        <v>548</v>
+      </c>
+      <c r="J138" s="34" t="s">
+        <v>548</v>
       </c>
       <c r="K138" s="34"/>
       <c r="L138" s="23" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="M138" s="23" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="N138" s="23" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="O138" s="23" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="P138" s="23" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="Q138" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="R138" s="23" t="s">
-        <v>140</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="R138" s="23"/>
       <c r="S138" s="23"/>
     </row>
     <row r="139" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="B139" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C139" s="36" t="s">
         <v>246</v>
       </c>
       <c r="D139" s="23" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="E139" s="23" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="F139" s="23" t="s">
         <v>500</v>
       </c>
       <c r="G139" s="23" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H139" s="23" t="s">
-        <v>69</v>
+        <v>557</v>
       </c>
       <c r="I139" s="34" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="J139" s="34" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K139" s="34"/>
       <c r="L139" s="23" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="M139" s="23" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N139" s="23" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="O139" s="23" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="P139" s="23" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="Q139" s="23" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="R139" s="23"/>
       <c r="S139" s="23"/>
     </row>
     <row r="140" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B140" s="22" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C140" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="D140" s="23" t="s">
-        <v>617</v>
+      <c r="D140" s="38" t="s">
+        <v>613</v>
       </c>
       <c r="E140" s="23" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F140" s="23" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G140" s="23" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H140" s="23" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="I140" s="34" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="J140" s="34" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="K140" s="34"/>
       <c r="L140" s="23" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="M140" s="23" t="s">
         <v>53</v>
       </c>
       <c r="N140" s="23" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="O140" s="23" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="P140" s="23" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="Q140" s="23" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R140" s="23"/>
       <c r="S140" s="23"/>
     </row>
-    <row r="141" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="B141" s="22" t="s">
-        <v>547</v>
-      </c>
-      <c r="C141" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="D141" s="38" t="s">
-        <v>616</v>
-      </c>
-      <c r="E141" s="23" t="s">
-        <v>537</v>
-      </c>
-      <c r="F141" s="23" t="s">
-        <v>501</v>
-      </c>
-      <c r="G141" s="23" t="s">
-        <v>586</v>
-      </c>
-      <c r="H141" s="23" t="s">
-        <v>557</v>
-      </c>
-      <c r="I141" s="34" t="s">
-        <v>552</v>
-      </c>
-      <c r="J141" s="34" t="s">
-        <v>552</v>
-      </c>
-      <c r="K141" s="34"/>
-      <c r="L141" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="M141" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="N141" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="O141" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="P141" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q141" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="R141" s="23"/>
-      <c r="S141" s="23"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S141">
-    <sortCondition ref="J2:J141"/>
-    <sortCondition ref="K2:K141"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S140">
+    <sortCondition ref="J2:J140"/>
+    <sortCondition ref="K2:K140"/>
   </sortState>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11210,25 +11146,25 @@
         <v>267</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>264</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="K1" s="10" t="s">
         <v>265</v>
@@ -11242,19 +11178,19 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>287</v>
@@ -11266,7 +11202,7 @@
         <v>62</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>289</v>
@@ -11279,22 +11215,22 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>57</v>
@@ -11306,7 +11242,7 @@
         <v>55</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -11314,19 +11250,19 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>166</v>
@@ -11349,22 +11285,22 @@
     </row>
     <row r="5" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>57</v>
@@ -11376,7 +11312,7 @@
         <v>80</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -11384,22 +11320,22 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>57</v>
@@ -11411,7 +11347,7 @@
         <v>96</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -11419,19 +11355,19 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>150</v>
@@ -11454,22 +11390,22 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>57</v>
@@ -11489,22 +11425,22 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>57</v>
@@ -11516,7 +11452,7 @@
         <v>80</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
@@ -11524,19 +11460,19 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>151</v>
@@ -11559,22 +11495,22 @@
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>57</v>
@@ -11586,7 +11522,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -11594,22 +11530,22 @@
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>57</v>
@@ -11629,22 +11565,22 @@
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>57</v>
@@ -11664,22 +11600,22 @@
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>57</v>
@@ -11691,7 +11627,7 @@
         <v>80</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -11699,22 +11635,22 @@
     </row>
     <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>57</v>
@@ -11726,7 +11662,7 @@
         <v>80</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
@@ -11734,22 +11670,22 @@
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>57</v>
@@ -11761,7 +11697,7 @@
         <v>80</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -11769,22 +11705,22 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>57</v>
@@ -11793,10 +11729,10 @@
         <v>56</v>
       </c>
       <c r="I17" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -11804,19 +11740,19 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>231</v>
@@ -11839,22 +11775,22 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>57</v>
@@ -11863,10 +11799,10 @@
         <v>56</v>
       </c>
       <c r="I19" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -11874,22 +11810,22 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>57</v>
@@ -11901,7 +11837,7 @@
         <v>80</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -11909,22 +11845,22 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>57</v>
@@ -11936,7 +11872,7 @@
         <v>80</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -11947,16 +11883,16 @@
         <v>207</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F22" s="20" t="s">
         <v>237</v>
@@ -11984,16 +11920,16 @@
         <v>201</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>228</v>
@@ -12018,22 +11954,22 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>57</v>
@@ -12058,16 +11994,16 @@
         <v>176</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>222</v>
@@ -12092,19 +12028,19 @@
     </row>
     <row r="26" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>286</v>
@@ -12119,7 +12055,7 @@
         <v>58</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
@@ -12132,16 +12068,16 @@
         <v>173</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>232</v>
@@ -12166,22 +12102,22 @@
     </row>
     <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>57</v>
@@ -12190,10 +12126,10 @@
         <v>56</v>
       </c>
       <c r="I28" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="J28" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -12204,16 +12140,16 @@
         <v>171</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="D29" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>229</v>
@@ -12241,16 +12177,16 @@
         <v>275</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="D30" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>152</v>
@@ -12273,22 +12209,22 @@
     </row>
     <row r="31" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>53</v>
@@ -12300,7 +12236,7 @@
         <v>58</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
@@ -12310,22 +12246,22 @@
     </row>
     <row r="32" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>53</v>
@@ -12337,7 +12273,7 @@
         <v>74</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
@@ -12350,16 +12286,16 @@
         <v>3</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>231</v>
@@ -12387,16 +12323,16 @@
         <v>306</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>237</v>
@@ -12422,16 +12358,16 @@
         <v>202</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>233</v>
@@ -12459,16 +12395,16 @@
         <v>310</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>309</v>
@@ -12483,7 +12419,7 @@
         <v>74</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -12491,19 +12427,19 @@
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>309</v>
@@ -12518,7 +12454,7 @@
         <v>74</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
@@ -12531,16 +12467,16 @@
         <v>198</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>216</v>
@@ -12588,7 +12524,7 @@
         <v>264</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>263</v>
@@ -12606,7 +12542,7 @@
         <v>268</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>257</v>
@@ -12615,16 +12551,16 @@
         <v>258</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="Q1" s="10" t="s">
         <v>265</v>
@@ -12779,16 +12715,16 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>270</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>312</v>
@@ -12814,20 +12750,20 @@
         <v>72</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>394</v>
       </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
     </row>
     <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>270</v>
@@ -12835,10 +12771,10 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>256</v>
@@ -12858,16 +12794,16 @@
         <v>2</v>
       </c>
       <c r="N33" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="O33" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="O33" s="3" t="s">
+      <c r="P33" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="P33" s="3" t="s">
+      <c r="Q33" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
@@ -12911,28 +12847,28 @@
         <v>267</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>487</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>264</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="L1" s="10" t="s">
         <v>265</v>
@@ -12946,10 +12882,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
@@ -12983,12 +12919,12 @@
         <v>186</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="15"/>
       <c r="E3" s="15" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F3" s="15" t="s">
         <v>241</v>
@@ -13016,15 +12952,15 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="16" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>221</v>
@@ -13052,15 +12988,15 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F5" s="15" t="s">
         <v>221</v>
@@ -13091,12 +13027,12 @@
         <v>301</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F6" s="15" t="s">
         <v>299</v>
@@ -13122,15 +13058,15 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="16" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F7" s="15" t="s">
         <v>221</v>
@@ -13158,15 +13094,15 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F8" s="15" t="s">
         <v>221</v>
@@ -13197,7 +13133,7 @@
         <v>197</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
@@ -13233,7 +13169,7 @@
         <v>251</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
@@ -13265,7 +13201,7 @@
         <v>200</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
@@ -13296,31 +13232,31 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
       <c r="F12" s="15" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H12" s="15" t="s">
         <v>84</v>
       </c>
       <c r="I12" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="J12" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="K12" s="15" t="s">
         <v>390</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>391</v>
       </c>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
@@ -13330,10 +13266,10 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
@@ -13364,10 +13300,10 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -13398,10 +13334,10 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -13433,7 +13369,7 @@
         <v>322</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
@@ -13465,7 +13401,7 @@
         <v>323</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
@@ -13499,7 +13435,7 @@
         <v>192</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -13530,10 +13466,10 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
@@ -13564,10 +13500,10 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
@@ -13601,7 +13537,7 @@
         <v>191</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
@@ -13635,7 +13571,7 @@
         <v>196</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -13669,19 +13605,19 @@
         <v>320</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>84</v>
@@ -13690,10 +13626,10 @@
         <v>72</v>
       </c>
       <c r="I23" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
